--- a/网站内容.xlsx
+++ b/网站内容.xlsx
@@ -1,56 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="主页" sheetId="1" r:id="rId1"/>
-    <sheet name="研究方向1" sheetId="2" r:id="rId2"/>
-    <sheet name="研究方向2" sheetId="3" r:id="rId3"/>
-    <sheet name="数据模型开源" sheetId="4" r:id="rId4"/>
-    <sheet name="平台系统" sheetId="5" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主页" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究方向1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究方向2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据模型开源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平台系统" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,229 +444,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>基本信息</v>
-      </c>
-      <c r="B1" t="str">
-        <v>研究方向：</v>
-      </c>
-      <c r="C1" t="str">
-        <v>教育经历</v>
-      </c>
-      <c r="D1" t="str">
-        <v>发表情况</v>
-      </c>
-      <c r="E1" t="str">
-        <v>项目</v>
-      </c>
-      <c r="F1" t="str">
-        <v>授课</v>
-      </c>
-      <c r="G1" t="str">
-        <v>学生</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str" xml:space="preserve">
-        <v xml:space="preserve">[姓名]，[职称]，[单位]
-导师：\href{https://example.com}{[导师姓名]}教授</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[方向1]：[具体描述]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[起止时间]，[学校]，[院系]，博士</v>
-      </c>
-      <c r="D2" t="str">
-        <v>\textbf{[姓名]}，[论文标题]，[期刊/会议]，[年份]</v>
-      </c>
-      <c r="E2" t="str">
-        <v>[项目名称]，[资助来源]，[角色]</v>
-      </c>
-      <c r="F2" t="str">
-        <v>[课程名]，[年份]</v>
-      </c>
-      <c r="G2" t="str">
-        <v>[招生/团队信息]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>基本信息</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>研究方向：</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>教育经历</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>发表情况</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>授课</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>德胜，本科生，上海交通大学外国语学院</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>对比语言学：日汉语言对比研究，包括语音、词汇、句法层面的跨语言分析</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022–至今，上海交通大学，外国语学院，本科</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>汉字文化圈的文字与语言交流研究，PRP大创，参与者（指导教师：李思齐）</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>photo.jpg</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[方向2]：[具体描述]</v>
-      </c>
-      <c r="C3" t="str">
-        <v>[起止时间]，[学校]，[院系]，硕士</v>
-      </c>
-      <c r="D3" t="str">
-        <v>\textbf{[姓名]}，[论文标题2]，[期刊/会议]，[年份]</v>
-      </c>
-      <c r="E3" t="str">
-        <v>[项目名称2]，[资助来源]</v>
-      </c>
-      <c r="F3" t="str">
-        <v>[课程名2]，[年份]</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>[起止时间]，[学校]，[专业]，学士</v>
-      </c>
-      <c r="D4" t="str">
-        <v>\textbf{[姓名]}，[论文标题3]，[期刊/会议]，[年份]</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>photo.jpg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>认知语义学：基于认知批评话语分析的媒体语料研究</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025.9–2026.2，大阪大学外国语学部，交换生</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[研究方向1标题]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[研究方向1子课题A]</v>
-      </c>
-      <c r="C1" t="str">
-        <v>[研究方向1子课题B]</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>[研究方向1的详细描述，可使用 \textbf{加粗} 和 \href{url}{链接}]</v>
-      </c>
-      <c r="B2" t="str" xml:space="preserve">
-        <v xml:space="preserve">[子课题A的描述]
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[研究方向1标题]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[研究方向1子课题A]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>[研究方向1子课题B]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[研究方向1的详细描述，可使用 \textbf{加粗} 和 \href{url}{链接}]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[子课题A的描述]
 &gt;[要点1]
-&gt;[要点2]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[子课题B的描述，\textit{斜体引用}]</v>
+&gt;[要点2]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[子课题B的描述，\textit{斜体引用}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>[相关PDF文件名].pdf</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[相关图片文件名].webp</v>
-      </c>
-      <c r="C3" t="str">
-        <v>[相关图片文件名].png</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[相关PDF文件名].pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[相关图片文件名].webp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[相关图片文件名].png</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[研究方向2标题]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[研究方向2子课题]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[研究方向2标题]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[研究方向2子课题]</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>[研究方向2的详细描述]</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[子课题描述，\href{https://example.com}{论文链接}]</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[研究方向2的详细描述]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[子课题描述，\href{https://example.com}{论文链接}]</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>[PDF文件名].pdf</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[PDF文件名2].pdf</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>[PDF文件名].pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[PDF文件名2].pdf</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>[数据集/模型1名称]</v>
-      </c>
-      <c r="B1" t="str">
-        <v>[数据集/模型2名称]</v>
-      </c>
-      <c r="C1" t="str">
-        <v>[数据集/模型3名称]</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>[数据集/模型1名称]</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[数据集/模型2名称]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>[数据集/模型3名称]</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>[数据集1描述]</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[数据集2描述]</v>
-      </c>
-      <c r="C2" t="str">
-        <v>[模型3描述]</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>[数据集1描述]</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[数据集2描述]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[模型3描述]</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/网站内容.xlsx
+++ b/网站内容.xlsx
@@ -1,33 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主页" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究方向1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究方向2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据模型开源" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="平台系统" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="主页" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -444,270 +396,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="50.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>基本信息</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>研究方向：</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>教育经历</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>发表情况</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>授课</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>学生</t>
-        </is>
+      <c r="A1" t="str">
+        <v>基本信息</v>
+      </c>
+      <c r="B1" t="str">
+        <v>研究方向</v>
+      </c>
+      <c r="C1" t="str">
+        <v>教育经历</v>
+      </c>
+      <c r="D1" t="str">
+        <v>发表情况</v>
+      </c>
+      <c r="E1" t="str">
+        <v>项目</v>
+      </c>
+      <c r="F1" t="str">
+        <v>动态</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>德胜，本科生，上海交通大学外国语学院</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>对比语言学：日汉语言对比研究，包括语音、词汇、句法层面的跨语言分析</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2022–至今，上海交通大学，外国语学院，本科</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>汉字文化圈的文字与语言交流研究，PRP大创，参与者（指导教师：李思齐）</t>
-        </is>
+      <c r="A2" t="str">
+        <v>德胜</v>
+      </c>
+      <c r="B2" t="str">
+        <v>对比语言学：日汉语言对比研究，包括语音、词汇、句法层面的跨语言分析</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2022–至今，上海交通大学，外国语学院，本科</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>汉字文化圈的文字与语言交流研究，PRP大创，参与者（指导教师：李思齐）</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>photo.jpg</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>认知语义学：基于认知批评话语分析的媒体语料研究</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025.9–2026.2，大阪大学外国语学部，交换生</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+      <c r="A3" t="str">
+        <v>本科生</v>
+      </c>
+      <c r="B3" t="str">
+        <v>认知语义学：基于认知批评话语分析的媒体语料研究</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2025.9–2026.2，大阪大学外国语学部，交换生</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>\href{https://www.sjtu.edu.cn}{上海交通大学外国语学院}</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>desheng@example.edu</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>photo.jpg</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>\href{https://github.com/wuyutanhongyuxin-cell}{GitHub}</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[研究方向1标题]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[研究方向1子课题A]</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>[研究方向1子课题B]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[研究方向1的详细描述，可使用 \textbf{加粗} 和 \href{url}{链接}]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[子课题A的描述]
-&gt;[要点1]
-&gt;[要点2]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[子课题B的描述，\textit{斜体引用}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[相关PDF文件名].pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[相关图片文件名].webp</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[相关图片文件名].png</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[研究方向2标题]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[研究方向2子课题]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[研究方向2的详细描述]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[子课题描述，\href{https://example.com}{论文链接}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[PDF文件名].pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[PDF文件名2].pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>[数据集/模型1名称]</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[数据集/模型2名称]</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>[数据集/模型3名称]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[数据集1描述]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[数据集2描述]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[模型3描述]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+  </ignoredErrors>
 </worksheet>
 </file>